--- a/Business Analysis/3.+Value-based+analysis_before.xlsx
+++ b/Business Analysis/3.+Value-based+analysis_before.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="B:\Courses\Video creating\Enterprise excellence\Case study\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\Financial-Analysis\Business Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DA969EC-16AC-4E6A-AE8F-094CFA10D3FF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BEA0D69-BDCD-47FE-AEAE-A457BA1496D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="4" xr2:uid="{F12A9117-8F43-4D89-91AA-57E2FEF63FB4}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" firstSheet="2" activeTab="4" xr2:uid="{F12A9117-8F43-4D89-91AA-57E2FEF63FB4}"/>
   </bookViews>
   <sheets>
     <sheet name="Database" sheetId="1" r:id="rId1"/>
@@ -267,13 +267,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -295,9 +294,9 @@
     <xf numFmtId="1" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -415,7 +414,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-GB"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -1119,6 +1118,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1126,7 +1126,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2056,23 +2055,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2368FC57-6F23-4732-A5C2-167A88E5ECC4}">
   <dimension ref="B1:L148"/>
-  <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="11.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
-    <col min="2" max="3" width="9.140625" style="1"/>
-    <col min="4" max="4" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" style="1"/>
-    <col min="6" max="6" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="9.1796875" style="1"/>
+    <col min="4" max="4" width="9.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.1796875" style="1"/>
+    <col min="6" max="6" width="12.453125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.42578125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="19.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="9" max="9" width="18.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.453125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="19.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2080,49 +2079,49 @@
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="9" t="s">
         <v>18</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="24" t="s">
+      <c r="F4" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="G4" s="24" t="s">
+      <c r="G4" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="H4" s="24" t="s">
+      <c r="H4" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="24" t="s">
+      <c r="I4" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="J4" s="24" t="s">
+      <c r="J4" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="24" t="s">
+      <c r="K4" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="L4" s="24" t="s">
+      <c r="L4" s="23" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B5" s="6">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B5" s="5">
         <v>1</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="5">
         <v>2019</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="10">
         <f>EOMONTH(DATE(C5,B5,"1"),0)</f>
         <v>43496</v>
       </c>
@@ -2151,14 +2150,14 @@
         <v>69.025004250191103</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B6" s="6">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B6" s="5">
         <v>2</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="5">
         <v>2019</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="10">
         <f>EOMONTH(DATE(C6,B6,"1"),0)</f>
         <v>43524</v>
       </c>
@@ -2187,14 +2186,14 @@
         <v>57.520836875159247</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B7" s="6">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B7" s="5">
         <v>3</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="5">
         <v>2019</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="10">
         <f>EOMONTH(DATE(C7,B7,"1"),0)</f>
         <v>43555</v>
       </c>
@@ -2223,14 +2222,14 @@
         <v>60.851039057917099</v>
       </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B8" s="6">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B8" s="5">
         <v>4</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="5">
         <v>2019</v>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="10">
         <f t="shared" ref="D8:D71" si="0">EOMONTH(DATE(C8,B8,"1"),0)</f>
         <v>43585</v>
       </c>
@@ -2259,14 +2258,14 @@
         <v>64.960981617215637</v>
       </c>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B9" s="6">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B9" s="5">
         <v>5</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="5">
         <v>2019</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="10">
         <f t="shared" si="0"/>
         <v>43616</v>
       </c>
@@ -2295,14 +2294,14 @@
         <v>64.960981617215637</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B10" s="6">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B10" s="5">
         <v>6</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="5">
         <v>2019</v>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="10">
         <f t="shared" si="0"/>
         <v>43646</v>
       </c>
@@ -2331,14 +2330,14 @@
         <v>71.706858378858712</v>
       </c>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B11" s="6">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B11" s="5">
         <v>7</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="5">
         <v>2019</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="10">
         <f t="shared" si="0"/>
         <v>43677</v>
       </c>
@@ -2367,14 +2366,14 @@
         <v>71.706858378858712</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B12" s="6">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B12" s="5">
         <v>8</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="5">
         <v>2019</v>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="10">
         <f t="shared" si="0"/>
         <v>43708</v>
       </c>
@@ -2403,14 +2402,14 @@
         <v>71.706858378858712</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B13" s="6">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B13" s="5">
         <v>9</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="5">
         <v>2019</v>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="10">
         <f t="shared" si="0"/>
         <v>43738</v>
       </c>
@@ -2439,14 +2438,14 @@
         <v>71.706858378858712</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B14" s="6">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B14" s="5">
         <v>10</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="5">
         <v>2019</v>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="10">
         <f t="shared" si="0"/>
         <v>43769</v>
       </c>
@@ -2475,14 +2474,14 @@
         <v>68.706787320924349</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B15" s="6">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B15" s="5">
         <v>11</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="5">
         <v>2019</v>
       </c>
-      <c r="D15" s="11">
+      <c r="D15" s="10">
         <f t="shared" si="0"/>
         <v>43799</v>
       </c>
@@ -2511,14 +2510,14 @@
         <v>68.706787320924349</v>
       </c>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B16" s="6">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B16" s="5">
         <v>12</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="5">
         <v>2019</v>
       </c>
-      <c r="D16" s="11">
+      <c r="D16" s="10">
         <f t="shared" si="0"/>
         <v>43830</v>
       </c>
@@ -2547,14 +2546,14 @@
         <v>68.706787320924349</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B17" s="6">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B17" s="5">
         <v>1</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="5">
         <v>2020</v>
       </c>
-      <c r="D17" s="11">
+      <c r="D17" s="10">
         <f t="shared" si="0"/>
         <v>43861</v>
       </c>
@@ -2583,14 +2582,14 @@
         <v>78.155624371879711</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B18" s="6">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B18" s="5">
         <v>2</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18" s="5">
         <v>2020</v>
       </c>
-      <c r="D18" s="11">
+      <c r="D18" s="10">
         <f t="shared" si="0"/>
         <v>43890</v>
       </c>
@@ -2619,14 +2618,14 @@
         <v>65.129686976566433</v>
       </c>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B19" s="6">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B19" s="5">
         <v>3</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19" s="5">
         <v>2020</v>
       </c>
-      <c r="D19" s="11">
+      <c r="D19" s="10">
         <f t="shared" si="0"/>
         <v>43921</v>
       </c>
@@ -2655,14 +2654,14 @@
         <v>75.274039028579637</v>
       </c>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B20" s="6">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B20" s="5">
         <v>4</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="5">
         <v>2020</v>
       </c>
-      <c r="D20" s="11">
+      <c r="D20" s="10">
         <f t="shared" si="0"/>
         <v>43951</v>
       </c>
@@ -2691,14 +2690,14 @@
         <v>75.274039028579637</v>
       </c>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B21" s="6">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B21" s="5">
         <v>5</v>
       </c>
-      <c r="C21" s="6">
+      <c r="C21" s="5">
         <v>2020</v>
       </c>
-      <c r="D21" s="11">
+      <c r="D21" s="10">
         <f t="shared" si="0"/>
         <v>43982</v>
       </c>
@@ -2727,14 +2726,14 @@
         <v>75.274039028579637</v>
       </c>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B22" s="6">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B22" s="5">
         <v>6</v>
       </c>
-      <c r="C22" s="6">
+      <c r="C22" s="5">
         <v>2020</v>
       </c>
-      <c r="D22" s="11">
+      <c r="D22" s="10">
         <f t="shared" si="0"/>
         <v>44012</v>
       </c>
@@ -2763,14 +2762,14 @@
         <v>84.321941536768662</v>
       </c>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B23" s="6">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B23" s="5">
         <v>7</v>
       </c>
-      <c r="C23" s="6">
+      <c r="C23" s="5">
         <v>2020</v>
       </c>
-      <c r="D23" s="11">
+      <c r="D23" s="10">
         <f t="shared" si="0"/>
         <v>44043</v>
       </c>
@@ -2799,14 +2798,14 @@
         <v>84.321941536768662</v>
       </c>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B24" s="6">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B24" s="5">
         <v>8</v>
       </c>
-      <c r="C24" s="6">
+      <c r="C24" s="5">
         <v>2020</v>
       </c>
-      <c r="D24" s="11">
+      <c r="D24" s="10">
         <f t="shared" si="0"/>
         <v>44074</v>
       </c>
@@ -2835,14 +2834,14 @@
         <v>84.321941536768662</v>
       </c>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="6">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B25" s="5">
         <v>9</v>
       </c>
-      <c r="C25" s="6">
+      <c r="C25" s="5">
         <v>2020</v>
       </c>
-      <c r="D25" s="11">
+      <c r="D25" s="10">
         <f t="shared" si="0"/>
         <v>44104</v>
       </c>
@@ -2871,14 +2870,14 @@
         <v>84.321941536768662</v>
       </c>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B26" s="6">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B26" s="5">
         <v>10</v>
       </c>
-      <c r="C26" s="6">
+      <c r="C26" s="5">
         <v>2020</v>
       </c>
-      <c r="D26" s="11">
+      <c r="D26" s="10">
         <f t="shared" si="0"/>
         <v>44135</v>
       </c>
@@ -2907,14 +2906,14 @@
         <v>76.996142597335265</v>
       </c>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B27" s="6">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B27" s="5">
         <v>11</v>
       </c>
-      <c r="C27" s="6">
+      <c r="C27" s="5">
         <v>2020</v>
       </c>
-      <c r="D27" s="11">
+      <c r="D27" s="10">
         <f t="shared" si="0"/>
         <v>44165</v>
       </c>
@@ -2943,14 +2942,14 @@
         <v>76.996142597335265</v>
       </c>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B28" s="6">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B28" s="5">
         <v>12</v>
       </c>
-      <c r="C28" s="6">
+      <c r="C28" s="5">
         <v>2020</v>
       </c>
-      <c r="D28" s="11">
+      <c r="D28" s="10">
         <f t="shared" si="0"/>
         <v>44196</v>
       </c>
@@ -2979,14 +2978,14 @@
         <v>80.67956081669594</v>
       </c>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B29" s="6">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B29" s="5">
         <v>1</v>
       </c>
-      <c r="C29" s="6">
+      <c r="C29" s="5">
         <v>2021</v>
       </c>
-      <c r="D29" s="11">
+      <c r="D29" s="10">
         <f t="shared" si="0"/>
         <v>44227</v>
       </c>
@@ -3015,14 +3014,14 @@
         <v>101.59504890398503</v>
       </c>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B30" s="6">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B30" s="5">
         <v>2</v>
       </c>
-      <c r="C30" s="6">
+      <c r="C30" s="5">
         <v>2021</v>
       </c>
-      <c r="D30" s="11">
+      <c r="D30" s="10">
         <f t="shared" si="0"/>
         <v>44255</v>
       </c>
@@ -3051,14 +3050,14 @@
         <v>85.647647017909222</v>
       </c>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B31" s="6">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B31" s="5">
         <v>3</v>
       </c>
-      <c r="C31" s="6">
+      <c r="C31" s="5">
         <v>2021</v>
       </c>
-      <c r="D31" s="11">
+      <c r="D31" s="10">
         <f t="shared" si="0"/>
         <v>44286</v>
       </c>
@@ -3087,14 +3086,14 @@
         <v>97.037630199114446</v>
       </c>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B32" s="6">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B32" s="5">
         <v>4</v>
       </c>
-      <c r="C32" s="6">
+      <c r="C32" s="5">
         <v>2021</v>
       </c>
-      <c r="D32" s="11">
+      <c r="D32" s="10">
         <f t="shared" si="0"/>
         <v>44316</v>
       </c>
@@ -3123,14 +3122,14 @@
         <v>98.916233982605618</v>
       </c>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B33" s="6">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B33" s="5">
         <v>5</v>
       </c>
-      <c r="C33" s="6">
+      <c r="C33" s="5">
         <v>2021</v>
       </c>
-      <c r="D33" s="11">
+      <c r="D33" s="10">
         <f t="shared" si="0"/>
         <v>44347</v>
       </c>
@@ -3159,14 +3158,14 @@
         <v>105.802493123179</v>
       </c>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B34" s="6">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B34" s="5">
         <v>6</v>
       </c>
-      <c r="C34" s="6">
+      <c r="C34" s="5">
         <v>2021</v>
       </c>
-      <c r="D34" s="11">
+      <c r="D34" s="10">
         <f t="shared" si="0"/>
         <v>44377</v>
       </c>
@@ -3195,14 +3194,14 @@
         <v>108.699557240416</v>
       </c>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B35" s="6">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B35" s="5">
         <v>7</v>
       </c>
-      <c r="C35" s="6">
+      <c r="C35" s="5">
         <v>2021</v>
       </c>
-      <c r="D35" s="11">
+      <c r="D35" s="10">
         <f t="shared" si="0"/>
         <v>44408</v>
       </c>
@@ -3231,14 +3230,14 @@
         <v>108.699557240416</v>
       </c>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B36" s="6">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B36" s="5">
         <v>8</v>
       </c>
-      <c r="C36" s="6">
+      <c r="C36" s="5">
         <v>2021</v>
       </c>
-      <c r="D36" s="11">
+      <c r="D36" s="10">
         <f t="shared" si="0"/>
         <v>44439</v>
       </c>
@@ -3267,14 +3266,14 @@
         <v>108.699557240416</v>
       </c>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B37" s="6">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B37" s="5">
         <v>9</v>
       </c>
-      <c r="C37" s="6">
+      <c r="C37" s="5">
         <v>2021</v>
       </c>
-      <c r="D37" s="11">
+      <c r="D37" s="10">
         <f t="shared" si="0"/>
         <v>44469</v>
       </c>
@@ -3303,14 +3302,14 @@
         <v>108.699557240416</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B38" s="6">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B38" s="5">
         <v>10</v>
       </c>
-      <c r="C38" s="6">
+      <c r="C38" s="5">
         <v>2021</v>
       </c>
-      <c r="D38" s="11">
+      <c r="D38" s="10">
         <f t="shared" si="0"/>
         <v>44500</v>
       </c>
@@ -3339,14 +3338,14 @@
         <v>102.40669860582705</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B39" s="6">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B39" s="5">
         <v>11</v>
       </c>
-      <c r="C39" s="6">
+      <c r="C39" s="5">
         <v>2021</v>
       </c>
-      <c r="D39" s="11">
+      <c r="D39" s="10">
         <f t="shared" si="0"/>
         <v>44530</v>
       </c>
@@ -3375,14 +3374,14 @@
         <v>102.40669860582705</v>
       </c>
     </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B40" s="6">
+    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B40" s="5">
         <v>12</v>
       </c>
-      <c r="C40" s="6">
+      <c r="C40" s="5">
         <v>2021</v>
       </c>
-      <c r="D40" s="11">
+      <c r="D40" s="10">
         <f t="shared" si="0"/>
         <v>44561</v>
       </c>
@@ -3411,14 +3410,14 @@
         <v>99.258185203903267</v>
       </c>
     </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B41" s="6">
+    <row r="41" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B41" s="5">
         <v>1</v>
       </c>
-      <c r="C41" s="6">
+      <c r="C41" s="5">
         <v>2019</v>
       </c>
-      <c r="D41" s="11">
+      <c r="D41" s="10">
         <f t="shared" si="0"/>
         <v>43496</v>
       </c>
@@ -3447,14 +3446,14 @@
         <v>2.9796847358460092</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B42" s="6">
+    <row r="42" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B42" s="5">
         <v>2</v>
       </c>
-      <c r="C42" s="6">
+      <c r="C42" s="5">
         <v>2019</v>
       </c>
-      <c r="D42" s="11">
+      <c r="D42" s="10">
         <f t="shared" si="0"/>
         <v>43524</v>
       </c>
@@ -3483,14 +3482,14 @@
         <v>3.2088912539880092</v>
       </c>
     </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B43" s="6">
+    <row r="43" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B43" s="5">
         <v>3</v>
       </c>
-      <c r="C43" s="6">
+      <c r="C43" s="5">
         <v>2019</v>
       </c>
-      <c r="D43" s="11">
+      <c r="D43" s="10">
         <f t="shared" si="0"/>
         <v>43555</v>
       </c>
@@ -3519,14 +3518,14 @@
         <v>3.7655356551900114</v>
       </c>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B44" s="6">
+    <row r="44" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B44" s="5">
         <v>4</v>
       </c>
-      <c r="C44" s="6">
+      <c r="C44" s="5">
         <v>2019</v>
       </c>
-      <c r="D44" s="11">
+      <c r="D44" s="10">
         <f t="shared" si="0"/>
         <v>43585</v>
       </c>
@@ -3555,14 +3554,14 @@
         <v>3.6673042902720114</v>
       </c>
     </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B45" s="6">
+    <row r="45" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B45" s="5">
         <v>5</v>
       </c>
-      <c r="C45" s="6">
+      <c r="C45" s="5">
         <v>2019</v>
       </c>
-      <c r="D45" s="11">
+      <c r="D45" s="10">
         <f t="shared" si="0"/>
         <v>43616</v>
       </c>
@@ -3591,14 +3590,14 @@
         <v>4.082058942148012</v>
       </c>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B46" s="6">
+    <row r="46" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B46" s="5">
         <v>6</v>
       </c>
-      <c r="C46" s="6">
+      <c r="C46" s="5">
         <v>2019</v>
       </c>
-      <c r="D46" s="11">
+      <c r="D46" s="10">
         <f t="shared" si="0"/>
         <v>43646</v>
       </c>
@@ -3627,14 +3626,14 @@
         <v>4.3221800563920132</v>
       </c>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B47" s="6">
+    <row r="47" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B47" s="5">
         <v>7</v>
       </c>
-      <c r="C47" s="6">
+      <c r="C47" s="5">
         <v>2019</v>
       </c>
-      <c r="D47" s="11">
+      <c r="D47" s="10">
         <f t="shared" si="0"/>
         <v>43677</v>
       </c>
@@ -3663,14 +3662,14 @@
         <v>4.3549238446980123</v>
       </c>
     </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B48" s="6">
+    <row r="48" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B48" s="5">
         <v>8</v>
       </c>
-      <c r="C48" s="6">
+      <c r="C48" s="5">
         <v>2019</v>
       </c>
-      <c r="D48" s="11">
+      <c r="D48" s="10">
         <f t="shared" si="0"/>
         <v>43708</v>
       </c>
@@ -3699,14 +3698,14 @@
         <v>3.0560869085600095</v>
       </c>
     </row>
-    <row r="49" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B49" s="6">
+    <row r="49" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B49" s="5">
         <v>9</v>
       </c>
-      <c r="C49" s="6">
+      <c r="C49" s="5">
         <v>2019</v>
       </c>
-      <c r="D49" s="11">
+      <c r="D49" s="10">
         <f t="shared" si="0"/>
         <v>43738</v>
       </c>
@@ -3735,14 +3734,14 @@
         <v>5.0425433991240149</v>
       </c>
     </row>
-    <row r="50" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B50" s="6">
+    <row r="50" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B50" s="5">
         <v>10</v>
       </c>
-      <c r="C50" s="6">
+      <c r="C50" s="5">
         <v>2019</v>
       </c>
-      <c r="D50" s="11">
+      <c r="D50" s="10">
         <f t="shared" si="0"/>
         <v>43769</v>
       </c>
@@ -3771,14 +3770,14 @@
         <v>5.0425433991240149</v>
       </c>
     </row>
-    <row r="51" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B51" s="6">
+    <row r="51" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B51" s="5">
         <v>11</v>
       </c>
-      <c r="C51" s="6">
+      <c r="C51" s="5">
         <v>2019</v>
       </c>
-      <c r="D51" s="11">
+      <c r="D51" s="10">
         <f t="shared" si="0"/>
         <v>43799</v>
       </c>
@@ -3807,14 +3806,14 @@
         <v>5.5227856276120155</v>
       </c>
     </row>
-    <row r="52" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B52" s="6">
+    <row r="52" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B52" s="5">
         <v>12</v>
       </c>
-      <c r="C52" s="6">
+      <c r="C52" s="5">
         <v>2019</v>
       </c>
-      <c r="D52" s="11">
+      <c r="D52" s="10">
         <f t="shared" si="0"/>
         <v>43830</v>
       </c>
@@ -3843,14 +3842,14 @@
         <v>5.7629067418560176</v>
       </c>
     </row>
-    <row r="53" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B53" s="6">
+    <row r="53" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B53" s="5">
         <v>1</v>
       </c>
-      <c r="C53" s="6">
+      <c r="C53" s="5">
         <v>2020</v>
       </c>
-      <c r="D53" s="11">
+      <c r="D53" s="10">
         <f t="shared" si="0"/>
         <v>43861</v>
       </c>
@@ -3879,14 +3878,14 @@
         <v>7.2522649846028084</v>
       </c>
     </row>
-    <row r="54" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B54" s="6">
+    <row r="54" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B54" s="5">
         <v>2</v>
       </c>
-      <c r="C54" s="6">
+      <c r="C54" s="5">
         <v>2020</v>
       </c>
-      <c r="D54" s="11">
+      <c r="D54" s="10">
         <f t="shared" si="0"/>
         <v>43890</v>
       </c>
@@ -3915,14 +3914,14 @@
         <v>6.8566868945335635</v>
       </c>
     </row>
-    <row r="55" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B55" s="6">
+    <row r="55" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B55" s="5">
         <v>3</v>
       </c>
-      <c r="C55" s="6">
+      <c r="C55" s="5">
         <v>2020</v>
       </c>
-      <c r="D55" s="11">
+      <c r="D55" s="10">
         <f t="shared" si="0"/>
         <v>43921</v>
       </c>
@@ -3951,14 +3950,14 @@
         <v>8.1884664644333505</v>
       </c>
     </row>
-    <row r="56" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B56" s="6">
+    <row r="56" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B56" s="5">
         <v>4</v>
       </c>
-      <c r="C56" s="6">
+      <c r="C56" s="5">
         <v>2020</v>
       </c>
-      <c r="D56" s="11">
+      <c r="D56" s="10">
         <f t="shared" si="0"/>
         <v>43951</v>
       </c>
@@ -3987,14 +3986,14 @@
         <v>7.3841243479592205</v>
       </c>
     </row>
-    <row r="57" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B57" s="6">
+    <row r="57" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B57" s="5">
         <v>5</v>
       </c>
-      <c r="C57" s="6">
+      <c r="C57" s="5">
         <v>2020</v>
       </c>
-      <c r="D57" s="11">
+      <c r="D57" s="10">
         <f t="shared" si="0"/>
         <v>43982</v>
       </c>
@@ -4023,14 +4022,14 @@
         <v>8.7950195358728571</v>
       </c>
     </row>
-    <row r="58" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B58" s="6">
+    <row r="58" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B58" s="5">
         <v>6</v>
       </c>
-      <c r="C58" s="6">
+      <c r="C58" s="5">
         <v>2020</v>
       </c>
-      <c r="D58" s="11">
+      <c r="D58" s="10">
         <f t="shared" si="0"/>
         <v>44012</v>
       </c>
@@ -4059,14 +4058,14 @@
         <v>8.7027179815233673</v>
       </c>
     </row>
-    <row r="59" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B59" s="6">
+    <row r="59" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B59" s="5">
         <v>7</v>
       </c>
-      <c r="C59" s="6">
+      <c r="C59" s="5">
         <v>2020</v>
       </c>
-      <c r="D59" s="11">
+      <c r="D59" s="10">
         <f t="shared" si="0"/>
         <v>44043</v>
       </c>
@@ -4095,14 +4094,14 @@
         <v>8.5840445545025919</v>
       </c>
     </row>
-    <row r="60" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B60" s="6">
+    <row r="60" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B60" s="5">
         <v>8</v>
       </c>
-      <c r="C60" s="6">
+      <c r="C60" s="5">
         <v>2020</v>
       </c>
-      <c r="D60" s="11">
+      <c r="D60" s="10">
         <f t="shared" si="0"/>
         <v>44074</v>
       </c>
@@ -4131,14 +4130,14 @@
         <v>5.907299478367376</v>
       </c>
     </row>
-    <row r="61" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B61" s="6">
+    <row r="61" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B61" s="5">
         <v>9</v>
       </c>
-      <c r="C61" s="6">
+      <c r="C61" s="5">
         <v>2020</v>
       </c>
-      <c r="D61" s="11">
+      <c r="D61" s="10">
         <f t="shared" si="0"/>
         <v>44104</v>
       </c>
@@ -4167,14 +4166,14 @@
         <v>9.1378538805995326</v>
       </c>
     </row>
-    <row r="62" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B62" s="6">
+    <row r="62" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B62" s="5">
         <v>10</v>
       </c>
-      <c r="C62" s="6">
+      <c r="C62" s="5">
         <v>2020</v>
       </c>
-      <c r="D62" s="11">
+      <c r="D62" s="10">
         <f t="shared" si="0"/>
         <v>44135</v>
       </c>
@@ -4203,14 +4202,14 @@
         <v>9.8630803790598129</v>
       </c>
     </row>
-    <row r="63" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B63" s="6">
+    <row r="63" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B63" s="5">
         <v>11</v>
       </c>
-      <c r="C63" s="6">
+      <c r="C63" s="5">
         <v>2020</v>
       </c>
-      <c r="D63" s="11">
+      <c r="D63" s="10">
         <f t="shared" si="0"/>
         <v>44165</v>
       </c>
@@ -4239,14 +4238,14 @@
         <v>10.153170978443926</v>
       </c>
     </row>
-    <row r="64" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B64" s="6">
+    <row r="64" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B64" s="5">
         <v>12</v>
       </c>
-      <c r="C64" s="6">
+      <c r="C64" s="5">
         <v>2020</v>
       </c>
-      <c r="D64" s="11">
+      <c r="D64" s="10">
         <f t="shared" si="0"/>
         <v>44196</v>
       </c>
@@ -4275,14 +4274,14 @@
         <v>9.96856786974495</v>
       </c>
     </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B65" s="6">
+    <row r="65" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B65" s="5">
         <v>1</v>
       </c>
-      <c r="C65" s="6">
+      <c r="C65" s="5">
         <v>2021</v>
       </c>
-      <c r="D65" s="11">
+      <c r="D65" s="10">
         <f t="shared" si="0"/>
         <v>44227</v>
       </c>
@@ -4311,14 +4310,14 @@
         <v>13.236524206212621</v>
       </c>
     </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B66" s="6">
+    <row r="66" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B66" s="5">
         <v>2</v>
       </c>
-      <c r="C66" s="6">
+      <c r="C66" s="5">
         <v>2021</v>
       </c>
-      <c r="D66" s="11">
+      <c r="D66" s="10">
         <f t="shared" si="0"/>
         <v>44255</v>
       </c>
@@ -4347,14 +4346,14 @@
         <v>11.821102698850286</v>
       </c>
     </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B67" s="6">
+    <row r="67" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B67" s="5">
         <v>3</v>
       </c>
-      <c r="C67" s="6">
+      <c r="C67" s="5">
         <v>2021</v>
       </c>
-      <c r="D67" s="11">
+      <c r="D67" s="10">
         <f t="shared" si="0"/>
         <v>44286</v>
       </c>
@@ -4383,14 +4382,14 @@
         <v>13.345402783702031</v>
       </c>
     </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B68" s="6">
+    <row r="68" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B68" s="5">
         <v>4</v>
       </c>
-      <c r="C68" s="6">
+      <c r="C68" s="5">
         <v>2021</v>
       </c>
-      <c r="D68" s="11">
+      <c r="D68" s="10">
         <f t="shared" si="0"/>
         <v>44316</v>
       </c>
@@ -4419,14 +4418,14 @@
         <v>13.065429298729258</v>
       </c>
     </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B69" s="6">
+    <row r="69" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B69" s="5">
         <v>5</v>
       </c>
-      <c r="C69" s="6">
+      <c r="C69" s="5">
         <v>2021</v>
       </c>
-      <c r="D69" s="11">
+      <c r="D69" s="10">
         <f t="shared" si="0"/>
         <v>44347</v>
       </c>
@@ -4455,14 +4454,14 @@
         <v>14.667499796073445</v>
       </c>
     </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B70" s="6">
+    <row r="70" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B70" s="5">
         <v>6</v>
       </c>
-      <c r="C70" s="6">
+      <c r="C70" s="5">
         <v>2021</v>
       </c>
-      <c r="D70" s="11">
+      <c r="D70" s="10">
         <f t="shared" si="0"/>
         <v>44377</v>
       </c>
@@ -4491,14 +4490,14 @@
         <v>13.718700763665721</v>
       </c>
     </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B71" s="6">
+    <row r="71" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B71" s="5">
         <v>7</v>
       </c>
-      <c r="C71" s="6">
+      <c r="C71" s="5">
         <v>2021</v>
       </c>
-      <c r="D71" s="11">
+      <c r="D71" s="10">
         <f t="shared" si="0"/>
         <v>44408</v>
       </c>
@@ -4527,14 +4526,14 @@
         <v>14.714162043568905</v>
       </c>
     </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B72" s="6">
+    <row r="72" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B72" s="5">
         <v>8</v>
       </c>
-      <c r="C72" s="6">
+      <c r="C72" s="5">
         <v>2021</v>
       </c>
-      <c r="D72" s="11">
+      <c r="D72" s="10">
         <f t="shared" ref="D72:D135" si="1">EOMONTH(DATE(C72,B72,"1"),0)</f>
         <v>44439</v>
       </c>
@@ -4563,14 +4562,14 @@
         <v>9.5813148190681225</v>
       </c>
     </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B73" s="6">
+    <row r="73" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B73" s="5">
         <v>9</v>
       </c>
-      <c r="C73" s="6">
+      <c r="C73" s="5">
         <v>2021</v>
       </c>
-      <c r="D73" s="11">
+      <c r="D73" s="10">
         <f t="shared" si="1"/>
         <v>44469</v>
       </c>
@@ -4599,14 +4598,14 @@
         <v>13.998674248638491</v>
       </c>
     </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B74" s="6">
+    <row r="74" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B74" s="5">
         <v>10</v>
       </c>
-      <c r="C74" s="6">
+      <c r="C74" s="5">
         <v>2021</v>
       </c>
-      <c r="D74" s="11">
+      <c r="D74" s="10">
         <f t="shared" si="1"/>
         <v>44500</v>
       </c>
@@ -4635,14 +4634,14 @@
         <v>16.45621928339947</v>
       </c>
     </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B75" s="6">
+    <row r="75" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B75" s="5">
         <v>11</v>
       </c>
-      <c r="C75" s="6">
+      <c r="C75" s="5">
         <v>2021</v>
       </c>
-      <c r="D75" s="11">
+      <c r="D75" s="10">
         <f t="shared" si="1"/>
         <v>44530</v>
       </c>
@@ -4671,14 +4670,14 @@
         <v>16.082921303435779</v>
       </c>
     </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B76" s="6">
+    <row r="76" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B76" s="5">
         <v>12</v>
       </c>
-      <c r="C76" s="6">
+      <c r="C76" s="5">
         <v>2021</v>
       </c>
-      <c r="D76" s="11">
+      <c r="D76" s="10">
         <f t="shared" si="1"/>
         <v>44561</v>
       </c>
@@ -4707,14 +4706,14 @@
         <v>15.678515158475117</v>
       </c>
     </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B77" s="6">
+    <row r="77" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B77" s="5">
         <v>1</v>
       </c>
-      <c r="C77" s="6">
+      <c r="C77" s="5">
         <v>2019</v>
       </c>
-      <c r="D77" s="11">
+      <c r="D77" s="10">
         <f t="shared" si="1"/>
         <v>43496</v>
       </c>
@@ -4743,14 +4742,14 @@
         <v>2.5124397260372198</v>
       </c>
     </row>
-    <row r="78" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B78" s="6">
+    <row r="78" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B78" s="5">
         <v>2</v>
       </c>
-      <c r="C78" s="6">
+      <c r="C78" s="5">
         <v>2019</v>
       </c>
-      <c r="D78" s="11">
+      <c r="D78" s="10">
         <f t="shared" si="1"/>
         <v>43524</v>
       </c>
@@ -4779,14 +4778,14 @@
         <v>2.7057043203477753</v>
       </c>
     </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B79" s="6">
+    <row r="79" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B79" s="5">
         <v>3</v>
       </c>
-      <c r="C79" s="6">
+      <c r="C79" s="5">
         <v>2019</v>
       </c>
-      <c r="D79" s="11">
+      <c r="D79" s="10">
         <f t="shared" si="1"/>
         <v>43555</v>
       </c>
@@ -4815,14 +4814,14 @@
         <v>3.1750611922448386</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B80" s="6">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B80" s="5">
         <v>4</v>
       </c>
-      <c r="C80" s="6">
+      <c r="C80" s="5">
         <v>2019</v>
       </c>
-      <c r="D80" s="11">
+      <c r="D80" s="10">
         <f t="shared" si="1"/>
         <v>43585</v>
       </c>
@@ -4851,14 +4850,14 @@
         <v>3.0922335089688859</v>
       </c>
     </row>
-    <row r="81" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B81" s="6">
+    <row r="81" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B81" s="5">
         <v>5</v>
       </c>
-      <c r="C81" s="6">
+      <c r="C81" s="5">
         <v>2019</v>
       </c>
-      <c r="D81" s="11">
+      <c r="D81" s="10">
         <f t="shared" si="1"/>
         <v>43616</v>
       </c>
@@ -4887,14 +4886,14 @@
         <v>3.4419503939117955</v>
       </c>
     </row>
-    <row r="82" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B82" s="6">
+    <row r="82" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B82" s="5">
         <v>6</v>
       </c>
-      <c r="C82" s="6">
+      <c r="C82" s="5">
         <v>2019</v>
       </c>
-      <c r="D82" s="11">
+      <c r="D82" s="10">
         <f t="shared" si="1"/>
         <v>43646</v>
       </c>
@@ -4923,14 +4922,14 @@
         <v>3.6444180641419015</v>
       </c>
     </row>
-    <row r="83" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B83" s="6">
+    <row r="83" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B83" s="5">
         <v>7</v>
       </c>
-      <c r="C83" s="6">
+      <c r="C83" s="5">
         <v>2019</v>
       </c>
-      <c r="D83" s="11">
+      <c r="D83" s="10">
         <f t="shared" si="1"/>
         <v>43677</v>
       </c>
@@ -4959,14 +4958,14 @@
         <v>3.6720272919005521</v>
       </c>
     </row>
-    <row r="84" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B84" s="6">
+    <row r="84" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B84" s="5">
         <v>8</v>
       </c>
-      <c r="C84" s="6">
+      <c r="C84" s="5">
         <v>2019</v>
       </c>
-      <c r="D84" s="11">
+      <c r="D84" s="10">
         <f t="shared" si="1"/>
         <v>43708</v>
       </c>
@@ -4995,14 +4994,14 @@
         <v>2.5768612574740724</v>
       </c>
     </row>
-    <row r="85" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B85" s="6">
+    <row r="85" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B85" s="5">
         <v>9</v>
       </c>
-      <c r="C85" s="6">
+      <c r="C85" s="5">
         <v>2019</v>
       </c>
-      <c r="D85" s="11">
+      <c r="D85" s="10">
         <f t="shared" si="1"/>
         <v>43738</v>
       </c>
@@ -5031,14 +5030,14 @@
         <v>4.2518210748322174</v>
       </c>
     </row>
-    <row r="86" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B86" s="6">
+    <row r="86" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B86" s="5">
         <v>10</v>
       </c>
-      <c r="C86" s="6">
+      <c r="C86" s="5">
         <v>2019</v>
       </c>
-      <c r="D86" s="11">
+      <c r="D86" s="10">
         <f t="shared" si="1"/>
         <v>43769</v>
       </c>
@@ -5067,14 +5066,14 @@
         <v>4.2518210748322174</v>
       </c>
     </row>
-    <row r="87" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B87" s="6">
+    <row r="87" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B87" s="5">
         <v>11</v>
       </c>
-      <c r="C87" s="6">
+      <c r="C87" s="5">
         <v>2019</v>
       </c>
-      <c r="D87" s="11">
+      <c r="D87" s="10">
         <f t="shared" si="1"/>
         <v>43799</v>
       </c>
@@ -5103,14 +5102,14 @@
         <v>4.6567564152924295</v>
       </c>
     </row>
-    <row r="88" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B88" s="6">
+    <row r="88" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B88" s="5">
         <v>12</v>
       </c>
-      <c r="C88" s="6">
+      <c r="C88" s="5">
         <v>2019</v>
       </c>
-      <c r="D88" s="11">
+      <c r="D88" s="10">
         <f t="shared" si="1"/>
         <v>43830</v>
       </c>
@@ -5139,14 +5138,14 @@
         <v>4.8592240855225359</v>
       </c>
     </row>
-    <row r="89" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B89" s="6">
+    <row r="89" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B89" s="5">
         <v>1</v>
       </c>
-      <c r="C89" s="6">
+      <c r="C89" s="5">
         <v>2020</v>
       </c>
-      <c r="D89" s="11">
+      <c r="D89" s="10">
         <f t="shared" si="1"/>
         <v>43861</v>
       </c>
@@ -5175,14 +5174,14 @@
         <v>5.9873962294839496</v>
       </c>
     </row>
-    <row r="90" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B90" s="6">
+    <row r="90" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B90" s="5">
         <v>2</v>
       </c>
-      <c r="C90" s="6">
+      <c r="C90" s="5">
         <v>2020</v>
       </c>
-      <c r="D90" s="11">
+      <c r="D90" s="10">
         <f t="shared" si="1"/>
         <v>43890</v>
       </c>
@@ -5211,14 +5210,14 @@
         <v>5.6608109806030038</v>
       </c>
     </row>
-    <row r="91" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B91" s="6">
+    <row r="91" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B91" s="5">
         <v>3</v>
       </c>
-      <c r="C91" s="6">
+      <c r="C91" s="5">
         <v>2020</v>
       </c>
-      <c r="D91" s="11">
+      <c r="D91" s="10">
         <f t="shared" si="1"/>
         <v>43921</v>
       </c>
@@ -5247,14 +5246,14 @@
         <v>6.7603146518355102</v>
       </c>
     </row>
-    <row r="92" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B92" s="6">
+    <row r="92" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B92" s="5">
         <v>4</v>
       </c>
-      <c r="C92" s="6">
+      <c r="C92" s="5">
         <v>2020</v>
       </c>
-      <c r="D92" s="11">
+      <c r="D92" s="10">
         <f t="shared" si="1"/>
         <v>43951</v>
       </c>
@@ -5283,14 +5282,14 @@
         <v>6.0962579791109262</v>
       </c>
     </row>
-    <row r="93" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B93" s="6">
+    <row r="93" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B93" s="5">
         <v>5</v>
       </c>
-      <c r="C93" s="6">
+      <c r="C93" s="5">
         <v>2020</v>
       </c>
-      <c r="D93" s="11">
+      <c r="D93" s="10">
         <f t="shared" si="1"/>
         <v>43982</v>
       </c>
@@ -5319,14 +5318,14 @@
         <v>7.2610787001196222</v>
       </c>
     </row>
-    <row r="94" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B94" s="6">
+    <row r="94" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B94" s="5">
         <v>6</v>
       </c>
-      <c r="C94" s="6">
+      <c r="C94" s="5">
         <v>2020</v>
       </c>
-      <c r="D94" s="11">
+      <c r="D94" s="10">
         <f t="shared" si="1"/>
         <v>44012</v>
       </c>
@@ -5355,14 +5354,14 @@
         <v>7.1848754753807356</v>
       </c>
     </row>
-    <row r="95" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B95" s="6">
+    <row r="95" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B95" s="5">
         <v>7</v>
       </c>
-      <c r="C95" s="6">
+      <c r="C95" s="5">
         <v>2020</v>
       </c>
-      <c r="D95" s="11">
+      <c r="D95" s="10">
         <f t="shared" si="1"/>
         <v>44043</v>
       </c>
@@ -5391,14 +5390,14 @@
         <v>7.0868999007164515</v>
       </c>
     </row>
-    <row r="96" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B96" s="6">
+    <row r="96" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B96" s="5">
         <v>8</v>
       </c>
-      <c r="C96" s="6">
+      <c r="C96" s="5">
         <v>2020</v>
       </c>
-      <c r="D96" s="11">
+      <c r="D96" s="10">
         <f t="shared" si="1"/>
         <v>44074</v>
       </c>
@@ -5427,14 +5426,14 @@
         <v>4.8770063832887409</v>
       </c>
     </row>
-    <row r="97" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B97" s="6">
+    <row r="97" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B97" s="5">
         <v>9</v>
       </c>
-      <c r="C97" s="6">
+      <c r="C97" s="5">
         <v>2020</v>
       </c>
-      <c r="D97" s="11">
+      <c r="D97" s="10">
         <f t="shared" si="1"/>
         <v>44104</v>
       </c>
@@ -5463,14 +5462,14 @@
         <v>7.5441192491497713</v>
       </c>
     </row>
-    <row r="98" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B98" s="6">
+    <row r="98" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B98" s="5">
         <v>10</v>
       </c>
-      <c r="C98" s="6">
+      <c r="C98" s="5">
         <v>2020</v>
       </c>
-      <c r="D98" s="11">
+      <c r="D98" s="10">
         <f t="shared" si="1"/>
         <v>44135</v>
       </c>
@@ -5499,14 +5498,14 @@
         <v>8.1428588720981647</v>
       </c>
     </row>
-    <row r="99" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B99" s="6">
+    <row r="99" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B99" s="5">
         <v>11</v>
       </c>
-      <c r="C99" s="6">
+      <c r="C99" s="5">
         <v>2020</v>
       </c>
-      <c r="D99" s="11">
+      <c r="D99" s="10">
         <f t="shared" si="1"/>
         <v>44165</v>
       </c>
@@ -5535,14 +5534,14 @@
         <v>8.382354721277526</v>
       </c>
     </row>
-    <row r="100" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B100" s="6">
+    <row r="100" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B100" s="5">
         <v>12</v>
       </c>
-      <c r="C100" s="6">
+      <c r="C100" s="5">
         <v>2020</v>
       </c>
-      <c r="D100" s="11">
+      <c r="D100" s="10">
         <f t="shared" si="1"/>
         <v>44196</v>
       </c>
@@ -5571,14 +5570,14 @@
         <v>8.2299482717997527</v>
       </c>
     </row>
-    <row r="101" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B101" s="6">
+    <row r="101" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B101" s="5">
         <v>1</v>
       </c>
-      <c r="C101" s="6">
+      <c r="C101" s="5">
         <v>2021</v>
       </c>
-      <c r="D101" s="11">
+      <c r="D101" s="10">
         <f t="shared" si="1"/>
         <v>44227</v>
       </c>
@@ -5607,14 +5606,14 @@
         <v>10.737220126311428</v>
       </c>
     </row>
-    <row r="102" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B102" s="6">
+    <row r="102" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B102" s="5">
         <v>2</v>
       </c>
-      <c r="C102" s="6">
+      <c r="C102" s="5">
         <v>2021</v>
       </c>
-      <c r="D102" s="11">
+      <c r="D102" s="10">
         <f t="shared" si="1"/>
         <v>44255</v>
       </c>
@@ -5643,14 +5642,14 @@
         <v>9.5890567520525085</v>
       </c>
     </row>
-    <row r="103" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B103" s="6">
+    <row r="103" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B103" s="5">
         <v>3</v>
       </c>
-      <c r="C103" s="6">
+      <c r="C103" s="5">
         <v>2021</v>
       </c>
-      <c r="D103" s="11">
+      <c r="D103" s="10">
         <f t="shared" si="1"/>
         <v>44286</v>
       </c>
@@ -5679,14 +5678,14 @@
         <v>10.825540385869804</v>
       </c>
     </row>
-    <row r="104" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B104" s="6">
+    <row r="104" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B104" s="5">
         <v>4</v>
       </c>
-      <c r="C104" s="6">
+      <c r="C104" s="5">
         <v>2021</v>
       </c>
-      <c r="D104" s="11">
+      <c r="D104" s="10">
         <f t="shared" si="1"/>
         <v>44316</v>
       </c>
@@ -5715,14 +5714,14 @@
         <v>10.598431147005403</v>
       </c>
     </row>
-    <row r="105" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B105" s="6">
+    <row r="105" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B105" s="5">
         <v>5</v>
       </c>
-      <c r="C105" s="6">
+      <c r="C105" s="5">
         <v>2021</v>
       </c>
-      <c r="D105" s="11">
+      <c r="D105" s="10">
         <f t="shared" si="1"/>
         <v>44347</v>
       </c>
@@ -5751,14 +5750,14 @@
         <v>11.898000680507254</v>
       </c>
     </row>
-    <row r="106" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B106" s="6">
+    <row r="106" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B106" s="5">
         <v>6</v>
       </c>
-      <c r="C106" s="6">
+      <c r="C106" s="5">
         <v>2021</v>
       </c>
-      <c r="D106" s="11">
+      <c r="D106" s="10">
         <f t="shared" si="1"/>
         <v>44377</v>
       </c>
@@ -5787,14 +5786,14 @@
         <v>11.128352704355672</v>
       </c>
     </row>
-    <row r="107" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B107" s="6">
+    <row r="107" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B107" s="5">
         <v>7</v>
       </c>
-      <c r="C107" s="6">
+      <c r="C107" s="5">
         <v>2021</v>
       </c>
-      <c r="D107" s="11">
+      <c r="D107" s="10">
         <f t="shared" si="1"/>
         <v>44408</v>
       </c>
@@ -5823,14 +5822,14 @@
         <v>11.935852220317987</v>
       </c>
     </row>
-    <row r="108" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B108" s="6">
+    <row r="108" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B108" s="5">
         <v>8</v>
       </c>
-      <c r="C108" s="6">
+      <c r="C108" s="5">
         <v>2021</v>
       </c>
-      <c r="D108" s="11">
+      <c r="D108" s="10">
         <f t="shared" si="1"/>
         <v>44439</v>
       </c>
@@ -5859,14 +5858,14 @@
         <v>7.772182841137294</v>
       </c>
     </row>
-    <row r="109" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B109" s="6">
+    <row r="109" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B109" s="5">
         <v>9</v>
       </c>
-      <c r="C109" s="6">
+      <c r="C109" s="5">
         <v>2021</v>
       </c>
-      <c r="D109" s="11">
+      <c r="D109" s="10">
         <f t="shared" si="1"/>
         <v>44469</v>
       </c>
@@ -5895,14 +5894,14 @@
         <v>11.355461943220073</v>
       </c>
     </row>
-    <row r="110" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B110" s="6">
+    <row r="110" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B110" s="5">
         <v>10</v>
       </c>
-      <c r="C110" s="6">
+      <c r="C110" s="5">
         <v>2021</v>
       </c>
-      <c r="D110" s="11">
+      <c r="D110" s="10">
         <f t="shared" si="1"/>
         <v>44500</v>
       </c>
@@ -5931,14 +5930,14 @@
         <v>13.348976373252041</v>
       </c>
     </row>
-    <row r="111" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B111" s="6">
+    <row r="111" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B111" s="5">
         <v>11</v>
       </c>
-      <c r="C111" s="6">
+      <c r="C111" s="5">
         <v>2021</v>
       </c>
-      <c r="D111" s="11">
+      <c r="D111" s="10">
         <f t="shared" si="1"/>
         <v>44530</v>
       </c>
@@ -5967,14 +5966,14 @@
         <v>13.046164054766171</v>
       </c>
     </row>
-    <row r="112" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B112" s="6">
+    <row r="112" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B112" s="5">
         <v>12</v>
       </c>
-      <c r="C112" s="6">
+      <c r="C112" s="5">
         <v>2021</v>
       </c>
-      <c r="D112" s="11">
+      <c r="D112" s="10">
         <f t="shared" si="1"/>
         <v>44561</v>
       </c>
@@ -6003,14 +6002,14 @@
         <v>12.718117376406488</v>
       </c>
     </row>
-    <row r="113" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B113" s="6">
+    <row r="113" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B113" s="5">
         <v>1</v>
       </c>
-      <c r="C113" s="6">
+      <c r="C113" s="5">
         <v>2019</v>
       </c>
-      <c r="D113" s="11">
+      <c r="D113" s="10">
         <f t="shared" si="1"/>
         <v>43496</v>
       </c>
@@ -6039,14 +6038,14 @@
         <v>5.0927506849621826</v>
       </c>
     </row>
-    <row r="114" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B114" s="6">
+    <row r="114" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B114" s="5">
         <v>2</v>
       </c>
-      <c r="C114" s="6">
+      <c r="C114" s="5">
         <v>2019</v>
       </c>
-      <c r="D114" s="11">
+      <c r="D114" s="10">
         <f t="shared" si="1"/>
         <v>43524</v>
       </c>
@@ -6075,14 +6074,14 @@
         <v>6.8111205198607507</v>
       </c>
     </row>
-    <row r="115" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B115" s="6">
+    <row r="115" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B115" s="5">
         <v>3</v>
       </c>
-      <c r="C115" s="6">
+      <c r="C115" s="5">
         <v>2019</v>
       </c>
-      <c r="D115" s="11">
+      <c r="D115" s="10">
         <f t="shared" si="1"/>
         <v>43555</v>
       </c>
@@ -6111,14 +6110,14 @@
         <v>10.312070251557737</v>
       </c>
     </row>
-    <row r="116" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B116" s="6">
+    <row r="116" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B116" s="5">
         <v>4</v>
       </c>
-      <c r="C116" s="6">
+      <c r="C116" s="5">
         <v>2019</v>
       </c>
-      <c r="D116" s="11">
+      <c r="D116" s="10">
         <f t="shared" si="1"/>
         <v>43585</v>
       </c>
@@ -6147,14 +6146,14 @@
         <v>9.0699708680454449</v>
       </c>
     </row>
-    <row r="117" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B117" s="6">
+    <row r="117" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B117" s="5">
         <v>5</v>
       </c>
-      <c r="C117" s="6">
+      <c r="C117" s="5">
         <v>2019</v>
       </c>
-      <c r="D117" s="11">
+      <c r="D117" s="10">
         <f t="shared" si="1"/>
         <v>43616</v>
       </c>
@@ -6183,14 +6182,14 @@
         <v>9.2450190868322792</v>
       </c>
     </row>
-    <row r="118" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B118" s="6">
+    <row r="118" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B118" s="5">
         <v>6</v>
       </c>
-      <c r="C118" s="6">
+      <c r="C118" s="5">
         <v>2019</v>
       </c>
-      <c r="D118" s="11">
+      <c r="D118" s="10">
         <f t="shared" si="1"/>
         <v>43646</v>
       </c>
@@ -6219,14 +6218,14 @@
         <v>9.4680150042305797</v>
       </c>
     </row>
-    <row r="119" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B119" s="6">
+    <row r="119" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B119" s="5">
         <v>7</v>
       </c>
-      <c r="C119" s="6">
+      <c r="C119" s="5">
         <v>2019</v>
       </c>
-      <c r="D119" s="11">
+      <c r="D119" s="10">
         <f t="shared" si="1"/>
         <v>43677</v>
       </c>
@@ -6255,14 +6254,14 @@
         <v>7.4921779038167768</v>
       </c>
     </row>
-    <row r="120" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B120" s="6">
+    <row r="120" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B120" s="5">
         <v>8</v>
       </c>
-      <c r="C120" s="6">
+      <c r="C120" s="5">
         <v>2019</v>
       </c>
-      <c r="D120" s="11">
+      <c r="D120" s="10">
         <f t="shared" si="1"/>
         <v>43708</v>
       </c>
@@ -6291,14 +6290,14 @@
         <v>5.3109476024213489</v>
       </c>
     </row>
-    <row r="121" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B121" s="6">
+    <row r="121" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B121" s="5">
         <v>9</v>
       </c>
-      <c r="C121" s="6">
+      <c r="C121" s="5">
         <v>2019</v>
       </c>
-      <c r="D121" s="11">
+      <c r="D121" s="10">
         <f t="shared" si="1"/>
         <v>43738</v>
       </c>
@@ -6327,14 +6326,14 @@
         <v>10.316668058759298</v>
       </c>
     </row>
-    <row r="122" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B122" s="6">
+    <row r="122" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B122" s="5">
         <v>10</v>
       </c>
-      <c r="C122" s="6">
+      <c r="C122" s="5">
         <v>2019</v>
       </c>
-      <c r="D122" s="11">
+      <c r="D122" s="10">
         <f t="shared" si="1"/>
         <v>43769</v>
       </c>
@@ -6363,14 +6362,14 @@
         <v>11.670156305808623</v>
       </c>
     </row>
-    <row r="123" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B123" s="6">
+    <row r="123" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B123" s="5">
         <v>11</v>
       </c>
-      <c r="C123" s="6">
+      <c r="C123" s="5">
         <v>2019</v>
       </c>
-      <c r="D123" s="11">
+      <c r="D123" s="10">
         <f t="shared" si="1"/>
         <v>43799</v>
       </c>
@@ -6399,14 +6398,14 @@
         <v>13.518131529598255</v>
       </c>
     </row>
-    <row r="124" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B124" s="6">
+    <row r="124" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B124" s="5">
         <v>12</v>
       </c>
-      <c r="C124" s="6">
+      <c r="C124" s="5">
         <v>2019</v>
       </c>
-      <c r="D124" s="11">
+      <c r="D124" s="10">
         <f t="shared" si="1"/>
         <v>43830</v>
       </c>
@@ -6435,14 +6434,14 @@
         <v>9.2735534923399623</v>
       </c>
     </row>
-    <row r="125" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B125" s="6">
+    <row r="125" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B125" s="5">
         <v>1</v>
       </c>
-      <c r="C125" s="6">
+      <c r="C125" s="5">
         <v>2020</v>
       </c>
-      <c r="D125" s="11">
+      <c r="D125" s="10">
         <f t="shared" si="1"/>
         <v>43861</v>
       </c>
@@ -6471,14 +6470,14 @@
         <v>6.7970741697009123</v>
       </c>
     </row>
-    <row r="126" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B126" s="6">
+    <row r="126" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B126" s="5">
         <v>2</v>
       </c>
-      <c r="C126" s="6">
+      <c r="C126" s="5">
         <v>2020</v>
       </c>
-      <c r="D126" s="11">
+      <c r="D126" s="10">
         <f t="shared" si="1"/>
         <v>43890</v>
       </c>
@@ -6507,14 +6506,14 @@
         <v>7.8578934918565615</v>
       </c>
     </row>
-    <row r="127" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B127" s="6">
+    <row r="127" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B127" s="5">
         <v>3</v>
       </c>
-      <c r="C127" s="6">
+      <c r="C127" s="5">
         <v>2020</v>
       </c>
-      <c r="D127" s="11">
+      <c r="D127" s="10">
         <f t="shared" si="1"/>
         <v>43921</v>
       </c>
@@ -6543,14 +6542,14 @@
         <v>12.641561343069679</v>
       </c>
     </row>
-    <row r="128" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B128" s="6">
+    <row r="128" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B128" s="5">
         <v>4</v>
       </c>
-      <c r="C128" s="6">
+      <c r="C128" s="5">
         <v>2020</v>
       </c>
-      <c r="D128" s="11">
+      <c r="D128" s="10">
         <f t="shared" si="1"/>
         <v>43951</v>
       </c>
@@ -6579,14 +6578,14 @@
         <v>10.568561460047512</v>
       </c>
     </row>
-    <row r="129" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B129" s="6">
+    <row r="129" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B129" s="5">
         <v>5</v>
       </c>
-      <c r="C129" s="6">
+      <c r="C129" s="5">
         <v>2020</v>
       </c>
-      <c r="D129" s="11">
+      <c r="D129" s="10">
         <f t="shared" si="1"/>
         <v>43982</v>
       </c>
@@ -6615,14 +6614,14 @@
         <v>11.784181002365107</v>
       </c>
     </row>
-    <row r="130" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B130" s="6">
+    <row r="130" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B130" s="5">
         <v>6</v>
       </c>
-      <c r="C130" s="6">
+      <c r="C130" s="5">
         <v>2020</v>
       </c>
-      <c r="D130" s="11">
+      <c r="D130" s="10">
         <f t="shared" si="1"/>
         <v>44012</v>
       </c>
@@ -6651,14 +6650,14 @@
         <v>11.50460052489913</v>
       </c>
     </row>
-    <row r="131" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B131" s="6">
+    <row r="131" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B131" s="5">
         <v>7</v>
       </c>
-      <c r="C131" s="6">
+      <c r="C131" s="5">
         <v>2020</v>
       </c>
-      <c r="D131" s="11">
+      <c r="D131" s="10">
         <f t="shared" si="1"/>
         <v>44043</v>
       </c>
@@ -6687,14 +6686,14 @@
         <v>9.0771045199016118</v>
       </c>
     </row>
-    <row r="132" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B132" s="6">
+    <row r="132" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B132" s="5">
         <v>8</v>
       </c>
-      <c r="C132" s="6">
+      <c r="C132" s="5">
         <v>2020</v>
       </c>
-      <c r="D132" s="11">
+      <c r="D132" s="10">
         <f t="shared" si="1"/>
         <v>44074</v>
       </c>
@@ -6723,14 +6722,14 @@
         <v>6.4156636052953733</v>
       </c>
     </row>
-    <row r="133" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B133" s="6">
+    <row r="133" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B133" s="5">
         <v>9</v>
       </c>
-      <c r="C133" s="6">
+      <c r="C133" s="5">
         <v>2020</v>
       </c>
-      <c r="D133" s="11">
+      <c r="D133" s="10">
         <f t="shared" si="1"/>
         <v>44104</v>
       </c>
@@ -6759,14 +6758,14 @@
         <v>11.908918774645899</v>
       </c>
     </row>
-    <row r="134" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B134" s="6">
+    <row r="134" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B134" s="5">
         <v>10</v>
       </c>
-      <c r="C134" s="6">
+      <c r="C134" s="5">
         <v>2020</v>
       </c>
-      <c r="D134" s="11">
+      <c r="D134" s="10">
         <f t="shared" si="1"/>
         <v>44135</v>
       </c>
@@ -6795,14 +6794,14 @@
         <v>14.53319806860838</v>
       </c>
     </row>
-    <row r="135" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B135" s="6">
+    <row r="135" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B135" s="5">
         <v>11</v>
       </c>
-      <c r="C135" s="6">
+      <c r="C135" s="5">
         <v>2020</v>
       </c>
-      <c r="D135" s="11">
+      <c r="D135" s="10">
         <f t="shared" si="1"/>
         <v>44165</v>
       </c>
@@ -6831,14 +6830,14 @@
         <v>16.188214233067796</v>
       </c>
     </row>
-    <row r="136" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B136" s="6">
+    <row r="136" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B136" s="5">
         <v>12</v>
       </c>
-      <c r="C136" s="6">
+      <c r="C136" s="5">
         <v>2020</v>
       </c>
-      <c r="D136" s="11">
+      <c r="D136" s="10">
         <f t="shared" ref="D136:D148" si="2">EOMONTH(DATE(C136,B136,"1"),0)</f>
         <v>44196</v>
       </c>
@@ -6867,14 +6866,14 @@
         <v>10.555823944863995</v>
       </c>
     </row>
-    <row r="137" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B137" s="6">
+    <row r="137" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B137" s="5">
         <v>1</v>
       </c>
-      <c r="C137" s="6">
+      <c r="C137" s="5">
         <v>2021</v>
       </c>
-      <c r="D137" s="11">
+      <c r="D137" s="10">
         <f t="shared" si="2"/>
         <v>44227</v>
       </c>
@@ -6903,14 +6902,14 @@
         <v>8.5315813046451812</v>
       </c>
     </row>
-    <row r="138" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B138" s="6">
+    <row r="138" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B138" s="5">
         <v>2</v>
       </c>
-      <c r="C138" s="6">
+      <c r="C138" s="5">
         <v>2021</v>
       </c>
-      <c r="D138" s="11">
+      <c r="D138" s="10">
         <f t="shared" si="2"/>
         <v>44255</v>
       </c>
@@ -6939,14 +6938,14 @@
         <v>9.1851774604645069</v>
       </c>
     </row>
-    <row r="139" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B139" s="6">
+    <row r="139" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B139" s="5">
         <v>3</v>
       </c>
-      <c r="C139" s="6">
+      <c r="C139" s="5">
         <v>2021</v>
       </c>
-      <c r="D139" s="11">
+      <c r="D139" s="10">
         <f t="shared" si="2"/>
         <v>44286</v>
       </c>
@@ -6975,14 +6974,14 @@
         <v>14.20201699623775</v>
       </c>
     </row>
-    <row r="140" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B140" s="6">
+    <row r="140" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B140" s="5">
         <v>4</v>
       </c>
-      <c r="C140" s="6">
+      <c r="C140" s="5">
         <v>2021</v>
       </c>
-      <c r="D140" s="11">
+      <c r="D140" s="10">
         <f t="shared" si="2"/>
         <v>44316</v>
       </c>
@@ -7011,14 +7010,14 @@
         <v>13.011753250517556</v>
       </c>
     </row>
-    <row r="141" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B141" s="6">
+    <row r="141" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B141" s="5">
         <v>5</v>
       </c>
-      <c r="C141" s="6">
+      <c r="C141" s="5">
         <v>2021</v>
       </c>
-      <c r="D141" s="11">
+      <c r="D141" s="10">
         <f t="shared" si="2"/>
         <v>44347</v>
       </c>
@@ -7047,14 +7046,14 @@
         <v>13.859429457000086</v>
       </c>
     </row>
-    <row r="142" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B142" s="6">
+    <row r="142" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B142" s="5">
         <v>6</v>
       </c>
-      <c r="C142" s="6">
+      <c r="C142" s="5">
         <v>2021</v>
       </c>
-      <c r="D142" s="11">
+      <c r="D142" s="10">
         <f t="shared" si="2"/>
         <v>44377</v>
       </c>
@@ -7083,14 +7082,14 @@
         <v>12.948386515999688</v>
       </c>
     </row>
-    <row r="143" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B143" s="6">
+    <row r="143" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B143" s="5">
         <v>7</v>
       </c>
-      <c r="C143" s="6">
+      <c r="C143" s="5">
         <v>2021</v>
       </c>
-      <c r="D143" s="11">
+      <c r="D143" s="10">
         <f t="shared" si="2"/>
         <v>44408</v>
       </c>
@@ -7119,14 +7118,14 @@
         <v>11.330204485253018</v>
       </c>
     </row>
-    <row r="144" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B144" s="6">
+    <row r="144" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B144" s="5">
         <v>8</v>
       </c>
-      <c r="C144" s="6">
+      <c r="C144" s="5">
         <v>2021</v>
       </c>
-      <c r="D144" s="11">
+      <c r="D144" s="10">
         <f t="shared" si="2"/>
         <v>44439</v>
       </c>
@@ -7155,14 +7154,14 @@
         <v>7.5916501755334727</v>
       </c>
     </row>
-    <row r="145" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B145" s="6">
+    <row r="145" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B145" s="5">
         <v>9</v>
       </c>
-      <c r="C145" s="6">
+      <c r="C145" s="5">
         <v>2021</v>
       </c>
-      <c r="D145" s="11">
+      <c r="D145" s="10">
         <f t="shared" si="2"/>
         <v>44469</v>
       </c>
@@ -7191,14 +7190,14 @@
         <v>13.506881481661727</v>
       </c>
     </row>
-    <row r="146" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B146" s="6">
+    <row r="146" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B146" s="5">
         <v>10</v>
       </c>
-      <c r="C146" s="6">
+      <c r="C146" s="5">
         <v>2021</v>
       </c>
-      <c r="D146" s="11">
+      <c r="D146" s="10">
         <f t="shared" si="2"/>
         <v>44500</v>
       </c>
@@ -7227,14 +7226,14 @@
         <v>17.881562291072846</v>
       </c>
     </row>
-    <row r="147" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B147" s="6">
+    <row r="147" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B147" s="5">
         <v>11</v>
       </c>
-      <c r="C147" s="6">
+      <c r="C147" s="5">
         <v>2021</v>
       </c>
-      <c r="D147" s="11">
+      <c r="D147" s="10">
         <f t="shared" si="2"/>
         <v>44530</v>
       </c>
@@ -7263,14 +7262,14 @@
         <v>19.271987850792122</v>
       </c>
     </row>
-    <row r="148" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B148" s="6">
+    <row r="148" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B148" s="5">
         <v>12</v>
       </c>
-      <c r="C148" s="6">
+      <c r="C148" s="5">
         <v>2021</v>
       </c>
-      <c r="D148" s="11">
+      <c r="D148" s="10">
         <f t="shared" si="2"/>
         <v>44561</v>
       </c>
@@ -7308,14 +7307,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17D5AA4B-FF51-4BA2-8284-F92416F83C9C}">
   <dimension ref="B15"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2" style="7" customWidth="1"/>
-    <col min="2" max="16384" width="9.140625" style="7"/>
+    <col min="1" max="1" width="2" style="6" customWidth="1"/>
+    <col min="2" max="16384" width="9.1796875" style="6"/>
   </cols>
   <sheetData>
-    <row r="15" spans="2:2" ht="50.25" x14ac:dyDescent="0.7">
-      <c r="B15" s="8" t="s">
+    <row r="15" spans="2:2" ht="50.5" x14ac:dyDescent="1">
+      <c r="B15" s="7" t="s">
         <v>15</v>
       </c>
     </row>
@@ -7328,458 +7327,457 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C5616EF-DC02-46F5-A8BF-BCC45ED435AB}">
   <dimension ref="B1:AN6"/>
-  <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="11.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="1"/>
-    <col min="3" max="3" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.1796875" style="1"/>
+    <col min="3" max="3" width="7.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.54296875" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="6.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="6.7265625" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="2" style="1" customWidth="1"/>
-    <col min="16" max="16" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="6.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="6.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="6.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="6.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="6.54296875" style="1" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="2" style="1" customWidth="1"/>
-    <col min="29" max="30" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="6.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="6.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="6.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="6.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="6.54296875" style="1" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="36" max="37" width="6.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="6.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="40" width="6.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:40" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:40" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B1" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
     </row>
-    <row r="4" spans="2:40" ht="12.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="9" t="s">
+    <row r="4" spans="2:40" ht="12" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="11">
         <v>43496</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="11">
         <v>43524</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="11">
         <v>43555</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="11">
         <v>43585</v>
       </c>
-      <c r="G4" s="12">
+      <c r="G4" s="11">
         <v>43616</v>
       </c>
-      <c r="H4" s="12">
+      <c r="H4" s="11">
         <v>43646</v>
       </c>
-      <c r="I4" s="12">
+      <c r="I4" s="11">
         <v>43677</v>
       </c>
-      <c r="J4" s="12">
+      <c r="J4" s="11">
         <v>43708</v>
       </c>
-      <c r="K4" s="12">
+      <c r="K4" s="11">
         <v>43738</v>
       </c>
-      <c r="L4" s="12">
+      <c r="L4" s="11">
         <v>43769</v>
       </c>
-      <c r="M4" s="12">
+      <c r="M4" s="11">
         <v>43799</v>
       </c>
-      <c r="N4" s="12">
+      <c r="N4" s="11">
         <v>43830</v>
       </c>
-      <c r="P4" s="12">
+      <c r="P4" s="11">
         <v>43861</v>
       </c>
-      <c r="Q4" s="12">
+      <c r="Q4" s="11">
         <v>43890</v>
       </c>
-      <c r="R4" s="12">
+      <c r="R4" s="11">
         <v>43921</v>
       </c>
-      <c r="S4" s="12">
+      <c r="S4" s="11">
         <v>43951</v>
       </c>
-      <c r="T4" s="12">
+      <c r="T4" s="11">
         <v>43982</v>
       </c>
-      <c r="U4" s="12">
+      <c r="U4" s="11">
         <v>44012</v>
       </c>
-      <c r="V4" s="12">
+      <c r="V4" s="11">
         <v>44043</v>
       </c>
-      <c r="W4" s="12">
+      <c r="W4" s="11">
         <v>44074</v>
       </c>
-      <c r="X4" s="12">
+      <c r="X4" s="11">
         <v>44104</v>
       </c>
-      <c r="Y4" s="12">
+      <c r="Y4" s="11">
         <v>44135</v>
       </c>
-      <c r="Z4" s="12">
+      <c r="Z4" s="11">
         <v>44165</v>
       </c>
-      <c r="AA4" s="12">
+      <c r="AA4" s="11">
         <v>44196</v>
       </c>
-      <c r="AC4" s="12">
+      <c r="AC4" s="11">
         <v>44227</v>
       </c>
-      <c r="AD4" s="12">
+      <c r="AD4" s="11">
         <v>44255</v>
       </c>
-      <c r="AE4" s="12">
+      <c r="AE4" s="11">
         <v>44286</v>
       </c>
-      <c r="AF4" s="12">
+      <c r="AF4" s="11">
         <v>44316</v>
       </c>
-      <c r="AG4" s="12">
+      <c r="AG4" s="11">
         <v>44347</v>
       </c>
-      <c r="AH4" s="12">
+      <c r="AH4" s="11">
         <v>44377</v>
       </c>
-      <c r="AI4" s="12">
+      <c r="AI4" s="11">
         <v>44408</v>
       </c>
-      <c r="AJ4" s="12">
+      <c r="AJ4" s="11">
         <v>44439</v>
       </c>
-      <c r="AK4" s="12">
+      <c r="AK4" s="11">
         <v>44469</v>
       </c>
-      <c r="AL4" s="12">
+      <c r="AL4" s="11">
         <v>44500</v>
       </c>
-      <c r="AM4" s="12">
+      <c r="AM4" s="11">
         <v>44530</v>
       </c>
-      <c r="AN4" s="12">
+      <c r="AN4" s="11">
         <v>44561</v>
       </c>
     </row>
-    <row r="5" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="13">
+      <c r="C5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!C$4,Database!$F:$F)</f>
         <v>1941.2307692307691</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!D$4,Database!$F:$F)</f>
         <v>1849.4690780228509</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!E$4,Database!$F:$F)</f>
         <v>2175.2769230769227</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!F$4,Database!$F:$F)</f>
         <v>2080.8114935648005</v>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!G$4,Database!$F:$F)</f>
         <v>2249.1230769230765</v>
       </c>
-      <c r="H5" s="13">
+      <c r="H5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!H$4,Database!$F:$F)</f>
         <v>2268.6</v>
       </c>
-      <c r="I5" s="13">
+      <c r="I5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!I$4,Database!$F:$F)</f>
         <v>2498.3076923076919</v>
       </c>
-      <c r="J5" s="13">
+      <c r="J5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!J$4,Database!$F:$F)</f>
         <v>1462.7392706420908</v>
       </c>
-      <c r="K5" s="13">
+      <c r="K5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!K$4,Database!$F:$F)</f>
         <v>2334.9230769230767</v>
       </c>
-      <c r="L5" s="13">
+      <c r="L5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!L$4,Database!$F:$F)</f>
         <v>2639.8615413642956</v>
       </c>
-      <c r="M5" s="13">
+      <c r="M5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!M$4,Database!$F:$F)</f>
         <v>2258.8321142992068</v>
       </c>
-      <c r="N5" s="13">
+      <c r="N5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!N$4,Database!$F:$F)</f>
         <v>2448.0830535688224</v>
       </c>
-      <c r="P5" s="13">
+      <c r="P5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!P$4,Database!$F:$F)</f>
         <v>2660.0985011616999</v>
       </c>
-      <c r="Q5" s="13">
+      <c r="Q5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!Q$4,Database!$F:$F)</f>
         <v>2301.820609688868</v>
       </c>
-      <c r="R5" s="13">
+      <c r="R5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!R$4,Database!$F:$F)</f>
         <v>2545.2376374103087</v>
       </c>
-      <c r="S5" s="13">
+      <c r="S5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!S$4,Database!$F:$F)</f>
         <v>2850.2724207650704</v>
       </c>
-      <c r="T5" s="13">
+      <c r="T5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!T$4,Database!$F:$F)</f>
         <v>3038.4310200419095</v>
       </c>
-      <c r="U5" s="13">
+      <c r="U5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!U$4,Database!$F:$F)</f>
         <v>3081.4457503043245</v>
       </c>
-      <c r="V5" s="13">
+      <c r="V5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!V$4,Database!$F:$F)</f>
         <v>3239.2990697390751</v>
       </c>
-      <c r="W5" s="13">
+      <c r="W5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!W$4,Database!$F:$F)</f>
         <v>1844.6118688762529</v>
       </c>
-      <c r="X5" s="13">
+      <c r="X5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!X$4,Database!$F:$F)</f>
         <v>2926.9243830603632</v>
       </c>
-      <c r="Y5" s="13">
+      <c r="Y5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!Y$4,Database!$F:$F)</f>
         <v>3382.5564278401821</v>
       </c>
-      <c r="Z5" s="13">
+      <c r="Z5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!Z$4,Database!$F:$F)</f>
         <v>3102.5376031076216</v>
       </c>
-      <c r="AA5" s="13">
+      <c r="AA5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!AA$4,Database!$F:$F)</f>
         <v>2853.3720012781246</v>
       </c>
-      <c r="AC5" s="13">
+      <c r="AC5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!AC$4,Database!$F:$F)</f>
         <v>3363.3852773606832</v>
       </c>
-      <c r="AD5" s="13">
+      <c r="AD5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!AD$4,Database!$F:$F)</f>
         <v>2896.4020535350955</v>
       </c>
-      <c r="AE5" s="13">
+      <c r="AE5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!AE$4,Database!$F:$F)</f>
         <v>3365.879258708992</v>
       </c>
-      <c r="AF5" s="13">
+      <c r="AF5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!AF$4,Database!$F:$F)</f>
         <v>3715.4704340513654</v>
       </c>
-      <c r="AG5" s="13">
+      <c r="AG5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!AG$4,Database!$F:$F)</f>
         <v>4039.0341221931335</v>
       </c>
-      <c r="AH5" s="13">
+      <c r="AH5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!AH$4,Database!$F:$F)</f>
         <v>3971.8638408805</v>
       </c>
-      <c r="AI5" s="13">
+      <c r="AI5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!AI$4,Database!$F:$F)</f>
         <v>4245.9215971449739</v>
       </c>
-      <c r="AJ5" s="13">
+      <c r="AJ5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!AJ$4,Database!$F:$F)</f>
         <v>2486.2807465538858</v>
       </c>
-      <c r="AK5" s="13">
+      <c r="AK5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!AK$4,Database!$F:$F)</f>
         <v>3863.1103827011807</v>
       </c>
-      <c r="AL5" s="13">
+      <c r="AL5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!AL$4,Database!$F:$F)</f>
         <v>4289.1516580473954</v>
       </c>
-      <c r="AM5" s="13">
+      <c r="AM5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!AM$4,Database!$F:$F)</f>
         <v>4193.7394584541544</v>
       </c>
-      <c r="AN5" s="13">
+      <c r="AN5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!AN$4,Database!$F:$F)</f>
         <v>3799.390432295012</v>
       </c>
     </row>
-    <row r="6" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="13">
+      <c r="C6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!C$4,Database!$G:$G)</f>
         <v>706.15384615384608</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!D$4,Database!$G:$G)</f>
         <v>600</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!E$4,Database!$G:$G)</f>
         <v>710.76923076923072</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!F$4,Database!$G:$G)</f>
         <v>656.30769230769238</v>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!G$4,Database!$G:$G)</f>
         <v>670.61538461538453</v>
       </c>
-      <c r="H6" s="13">
+      <c r="H6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!H$4,Database!$G:$G)</f>
         <v>593.53846153846155</v>
       </c>
-      <c r="I6" s="13">
+      <c r="I6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!I$4,Database!$G:$G)</f>
         <v>583.38461538461536</v>
       </c>
-      <c r="J6" s="13">
+      <c r="J6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!J$4,Database!$G:$G)</f>
         <v>474.46153846153845</v>
       </c>
-      <c r="K6" s="13">
+      <c r="K6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!K$4,Database!$G:$G)</f>
         <v>639.69230769230762</v>
       </c>
-      <c r="L6" s="13">
+      <c r="L6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!L$4,Database!$G:$G)</f>
         <v>676.61538461538453</v>
       </c>
-      <c r="M6" s="13">
+      <c r="M6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!M$4,Database!$G:$G)</f>
         <v>571.38461538461536</v>
       </c>
-      <c r="N6" s="13">
+      <c r="N6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!N$4,Database!$G:$G)</f>
         <v>422.76923076923066</v>
       </c>
-      <c r="P6" s="13">
+      <c r="P6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!P$4,Database!$G:$G)</f>
         <v>596.71949207527507</v>
       </c>
-      <c r="Q6" s="13">
+      <c r="Q6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!Q$4,Database!$G:$G)</f>
         <v>504.42901070568638</v>
       </c>
-      <c r="R6" s="13">
+      <c r="R6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!R$4,Database!$G:$G)</f>
         <v>596.36058786890646</v>
       </c>
-      <c r="S6" s="13">
+      <c r="S6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!S$4,Database!$G:$G)</f>
         <v>726.58170848780583</v>
       </c>
-      <c r="T6" s="13">
+      <c r="T6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!T$4,Database!$G:$G)</f>
         <v>705.03445476861111</v>
       </c>
-      <c r="U6" s="13">
+      <c r="U6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!U$4,Database!$G:$G)</f>
         <v>683.74813890747942</v>
       </c>
-      <c r="V6" s="13">
+      <c r="V6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!V$4,Database!$G:$G)</f>
         <v>612.10540577172105</v>
       </c>
-      <c r="W6" s="13">
+      <c r="W6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!W$4,Database!$G:$G)</f>
         <v>509.49498696850935</v>
       </c>
-      <c r="X6" s="13">
+      <c r="X6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!X$4,Database!$G:$G)</f>
         <v>716.91889176476468</v>
       </c>
-      <c r="Y6" s="13">
+      <c r="Y6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!Y$4,Database!$G:$G)</f>
         <v>731.14755311591955</v>
       </c>
-      <c r="Z6" s="13">
+      <c r="Z6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!Z$4,Database!$G:$G)</f>
         <v>590.71973108505404</v>
       </c>
-      <c r="AA6" s="13">
+      <c r="AA6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!AA$4,Database!$G:$G)</f>
         <v>589.9854844016553</v>
       </c>
-      <c r="AC6" s="13">
+      <c r="AC6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!AC$4,Database!$G:$G)</f>
         <v>830.40526365672724</v>
       </c>
-      <c r="AD6" s="13">
+      <c r="AD6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!AD$4,Database!$G:$G)</f>
         <v>681.69872570104417</v>
       </c>
-      <c r="AE6" s="13">
+      <c r="AE6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!AE$4,Database!$G:$G)</f>
         <v>881.25703792407626</v>
       </c>
-      <c r="AF6" s="13">
+      <c r="AF6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!AF$4,Database!$G:$G)</f>
         <v>962.77009739234722</v>
       </c>
-      <c r="AG6" s="13">
+      <c r="AG6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!AG$4,Database!$G:$G)</f>
         <v>984.26685700500332</v>
       </c>
-      <c r="AH6" s="13">
+      <c r="AH6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!AH$4,Database!$G:$G)</f>
         <v>892.57693620058262</v>
       </c>
-      <c r="AI6" s="13">
+      <c r="AI6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!AI$4,Database!$G:$G)</f>
         <v>849.00258706451814</v>
       </c>
-      <c r="AJ6" s="13">
+      <c r="AJ6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!AJ$4,Database!$G:$G)</f>
         <v>651.03464179819332</v>
       </c>
-      <c r="AK6" s="13">
+      <c r="AK6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!AK$4,Database!$G:$G)</f>
         <v>969.92134547183161</v>
       </c>
-      <c r="AL6" s="13">
+      <c r="AL6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!AL$4,Database!$G:$G)</f>
         <v>912.00556711908484</v>
       </c>
-      <c r="AM6" s="13">
+      <c r="AM6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!AM$4,Database!$G:$G)</f>
         <v>886.19585760204654</v>
       </c>
-      <c r="AN6" s="13">
+      <c r="AN6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!AN$4,Database!$G:$G)</f>
         <v>799.51580878156631</v>
       </c>
@@ -7794,25 +7792,25 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6806D4A5-53CC-4EE4-9048-325F21B2D152}">
   <dimension ref="B1:H8"/>
-  <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="11.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="1"/>
-    <col min="3" max="3" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="1"/>
+    <col min="2" max="2" width="9.1796875" style="1"/>
+    <col min="3" max="3" width="7.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B1" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C3" s="1">
         <v>2020</v>
       </c>
@@ -7826,105 +7824,105 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="12.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="9" t="s">
+    <row r="4" spans="2:8" ht="12" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="13">
+      <c r="C5" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$C:$C,'2. Comparative analysis'!C$3,Database!$E:$E,'2. Comparative analysis'!C$4)</f>
         <v>28425.842968554865</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$C:$C,'2. Comparative analysis'!D$3,Database!$E:$E,'2. Comparative analysis'!D$4)</f>
         <v>1453.8325384615384</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$C:$C,'2. Comparative analysis'!E$3,Database!$E:$E,'2. Comparative analysis'!E$4)</f>
         <v>2527.9539230769228</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$C:$C,'2. Comparative analysis'!F$3,Database!$E:$E,'2. Comparative analysis'!F$4)</f>
         <v>1418.97786318047</v>
       </c>
-      <c r="H5" s="13"/>
-    </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H5" s="12"/>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="13">
+      <c r="C6" s="12">
         <f>SUMIFS(Database!$G:$G,Database!$C:$C,'2. Comparative analysis'!C$3,Database!$E:$E,'2. Comparative analysis'!C$4)</f>
         <v>-5741.8060487947223</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="12">
         <f>SUMIFS(Database!$G:$G,Database!$C:$C,'2. Comparative analysis'!D$3,Database!$E:$E,'2. Comparative analysis'!D$4)</f>
         <v>-365.53846153846149</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="12">
         <f>SUMIFS(Database!$G:$G,Database!$C:$C,'2. Comparative analysis'!E$3,Database!$E:$E,'2. Comparative analysis'!E$4)</f>
         <v>-475.38461538461524</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="12">
         <f>SUMIFS(Database!$G:$G,Database!$C:$C,'2. Comparative analysis'!F$3,Database!$E:$E,'2. Comparative analysis'!F$4)</f>
         <v>-980.51632020358954</v>
       </c>
-      <c r="H6" s="13"/>
-    </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H6" s="12"/>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="13">
+      <c r="C7" s="12">
         <f>SUM(C5:C6)</f>
         <v>22684.036919760143</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="12">
         <f t="shared" ref="D7:F7" si="0">SUM(D5:D6)</f>
         <v>1088.294076923077</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="12">
         <f t="shared" si="0"/>
         <v>2052.5693076923076</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="12">
         <f t="shared" si="0"/>
         <v>438.46154297688042</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B8" s="15" t="s">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B8" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="16">
+      <c r="C8" s="15">
         <f>C7/C5</f>
         <v>0.79800753648198219</v>
       </c>
-      <c r="D8" s="16">
+      <c r="D8" s="15">
         <f>D7/D5</f>
         <v>0.74856907390085092</v>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="15">
         <f>E7/E5</f>
         <v>0.81194886067939231</v>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="15">
         <f>F7/F5</f>
         <v>0.3089981558937932</v>
       </c>
@@ -7938,52 +7936,52 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E17FCAD-CCDF-436D-9A7D-9C663632857A}">
   <dimension ref="B1:E12"/>
-  <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="11.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
     <col min="2" max="2" width="16" style="1" customWidth="1"/>
-    <col min="3" max="5" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="3" max="5" width="9.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B1" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
     </row>
-    <row r="4" spans="2:5" ht="12.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="9" t="s">
+    <row r="4" spans="2:5" ht="12" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="13" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="13">
+      <c r="C5" s="12">
         <f>1.1*D5</f>
         <v>23256.062500000004</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="12">
         <v>21141.875</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="12">
         <f>D5*0.85</f>
         <v>17970.59375</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>25</v>
       </c>
@@ -7997,49 +7995,76 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B7" s="17" t="s">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B7" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B8" s="22"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="23"/>
-    </row>
-    <row r="9" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="5" t="s">
+      <c r="C7" s="17">
+        <f>C5*C6</f>
+        <v>32558.487500000003</v>
+      </c>
+      <c r="D7" s="17">
+        <f>D5*D6</f>
+        <v>33827</v>
+      </c>
+      <c r="E7" s="17">
+        <f>E5*E6</f>
+        <v>32347.068750000002</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="21"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="21">
+      <c r="C9" s="20">
         <v>-0.33</v>
       </c>
-      <c r="D9" s="21">
+      <c r="D9" s="20">
         <v>-0.35</v>
       </c>
-      <c r="E9" s="21">
+      <c r="E9" s="20">
         <v>-0.39</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B10" s="17" t="s">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-    </row>
-    <row r="12" spans="2:5" ht="12.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="19" t="s">
+      <c r="C10" s="17">
+        <f>C5*C9</f>
+        <v>-7674.5006250000015</v>
+      </c>
+      <c r="D10" s="17">
+        <f t="shared" ref="D10:E10" si="0">D5*D9</f>
+        <v>-7399.6562499999991</v>
+      </c>
+      <c r="E10" s="17">
+        <f t="shared" si="0"/>
+        <v>-7008.5315625000003</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" ht="12" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="20"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
+      <c r="C12" s="19">
+        <f>C7+C10</f>
+        <v>24883.986875000002</v>
+      </c>
+      <c r="D12" s="19">
+        <f t="shared" ref="D12:E12" si="1">D7+D10</f>
+        <v>26427.34375</v>
+      </c>
+      <c r="E12" s="19">
+        <f t="shared" si="1"/>
+        <v>25338.537187500002</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
